--- a/PS-VRP/Dati_output/Problemi_incompatibilità.xlsx
+++ b/PS-VRP/Dati_output/Problemi_incompatibilità.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,9 +442,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>254339</v>
+        <v>252466</v>
       </c>
       <c r="B2" t="inlineStr">
+        <is>
+          <t>nessuna compatibilità con alcuna macchina</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>252418</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nessuna compatibilità con alcuna macchina</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>252417</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nessuna compatibilità con alcuna macchina</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>252980</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>nessuna compatibilità con alcuna macchina</t>
         </is>
